--- a/data/kg_toolkit.xlsx
+++ b/data/kg_toolkit.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dictionary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cq" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="suppliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bom" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="specs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchases" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lots" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lot_operations" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lot_parts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inspections" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maintenance" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orders_shipments" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defects" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="dictionary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="rules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cq" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="products" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="parts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="suppliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="customers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="bom" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="equipment" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="specs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="purchases" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="lots" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="lot_operations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="lot_parts" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="inspections" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="maintenance" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="orders_shipments" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="defects" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,10 +34,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -93,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,7 +104,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6094,7 +6094,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>46144.375</v>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>46149.375</v>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>46150.375</v>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
           <t>E004</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>46150.375</v>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
           <t>E005</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>46152.375</v>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
           <t>E006</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>46154.375</v>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
           <t>E007</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>46154.375</v>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>46154.375</v>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
           <t>E009</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>46155.375</v>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
           <t>E010</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>46155.375</v>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
           <t>E011</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>46156.375</v>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
           <t>E012</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>46158.375</v>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>46159.375</v>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
           <t>E014</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>46160.375</v>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
           <t>E015</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>46161.375</v>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>46163.375</v>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>46166.375</v>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>46169.375</v>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
           <t>E004</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>46170.375</v>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
           <t>E005</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>46170.375</v>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
           <t>E006</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>46171.375</v>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
           <t>E007</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>46174.375</v>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>46175.375</v>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
           <t>E009</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="8" t="n">
         <v>46176.375</v>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
           <t>E010</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="8" t="n">
         <v>46177.375</v>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
           <t>E011</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="8" t="n">
         <v>46178.375</v>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
           <t>E012</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="8" t="n">
         <v>46182.375</v>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>46188.375</v>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
           <t>E014</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>46188.375</v>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
           <t>E015</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>46188.375</v>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="8" t="n">
         <v>46192.375</v>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="8" t="n">
         <v>46192.375</v>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>46193.375</v>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
           <t>E004</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>46193.375</v>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
           <t>E005</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>46199.375</v>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
           <t>E006</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>46199.375</v>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
           <t>E007</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="8" t="n">
         <v>46201.375</v>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="8" t="n">
         <v>46203.375</v>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
           <t>E009</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>46206.375</v>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
           <t>E010</t>
         </is>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>46212.375</v>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
           <t>E011</t>
         </is>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>46212.375</v>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
           <t>E012</t>
         </is>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="8" t="n">
         <v>46213.375</v>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>46213.375</v>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
           <t>E014</t>
         </is>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>46214.375</v>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
           <t>E015</t>
         </is>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>46214.375</v>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>46215.375</v>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>46216.375</v>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>46218.375</v>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
           <t>E004</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>46219.375</v>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
           <t>E005</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>46220.375</v>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
           <t>E006</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="8" t="n">
         <v>46220.375</v>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
           <t>E007</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>46221.375</v>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="8" t="n">
         <v>46223.375</v>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
           <t>E009</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="8" t="n">
         <v>46224.375</v>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
           <t>E010</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="8" t="n">
         <v>46226.375</v>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
           <t>E011</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="8" t="n">
         <v>46226.375</v>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
           <t>E012</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="8" t="n">
         <v>46227.375</v>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="8" t="n">
         <v>46228.375</v>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
           <t>E014</t>
         </is>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="8" t="n">
         <v>46230.375</v>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
           <t>E015</t>
         </is>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="8" t="n">
         <v>46232.375</v>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="8" t="n">
         <v>46234.375</v>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="8" t="n">
         <v>46241.375</v>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="8" t="n">
         <v>46241.375</v>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
           <t>E004</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="8" t="n">
         <v>46242.375</v>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
           <t>E005</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="8" t="n">
         <v>46245.375</v>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
           <t>E006</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="8" t="n">
         <v>46246.375</v>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
           <t>E007</t>
         </is>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="8" t="n">
         <v>46247.375</v>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="8" t="n">
         <v>46250.375</v>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
           <t>E009</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F70" s="8" t="n">
         <v>46253.375</v>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
           <t>E010</t>
         </is>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="8" t="n">
         <v>46253.375</v>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
           <t>E011</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F72" s="8" t="n">
         <v>46256.375</v>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
           <t>E012</t>
         </is>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="8" t="n">
         <v>46256.375</v>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="8" t="n">
         <v>46257.375</v>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
           <t>E014</t>
         </is>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F75" s="8" t="n">
         <v>46258.375</v>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="8" t="n">
         <v>46259.375</v>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F77" s="7" t="n">
+      <c r="F77" s="8" t="n">
         <v>46260.375</v>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="8" t="n">
         <v>46263.375</v>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F79" s="8" t="n">
         <v>46264.375</v>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F80" s="8" t="n">
         <v>46265.375</v>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="F81" s="7" t="n">
+      <c r="F81" s="8" t="n">
         <v>46268.375</v>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>46146.625</v>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>46151.625</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>46152.625</v>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>46155.625</v>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>46156.625</v>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>46156.625</v>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>46159.625</v>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>46157.625</v>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>46158.625</v>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>46159.625</v>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>46160.625</v>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>46161.625</v>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>46164.625</v>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>46164.625</v>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>46166.625</v>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>46168.625</v>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>46171.625</v>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>46173.625</v>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>46175.625</v>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>46175.625</v>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>46173.625</v>
       </c>
     </row>
@@ -10618,7 +10618,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>46178.625</v>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>46177.625</v>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="8" t="n">
         <v>46180.625</v>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="8" t="n">
         <v>46182.625</v>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="8" t="n">
         <v>46181.625</v>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="8" t="n">
         <v>46185.625</v>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>46193.625</v>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>46192.625</v>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>46192.625</v>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="8" t="n">
         <v>46197.625</v>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="8" t="n">
         <v>46197.625</v>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>46197.625</v>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>46196.625</v>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>46202.625</v>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>46204.625</v>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="8" t="n">
         <v>46204.625</v>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="8" t="n">
         <v>46207.625</v>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>46210.625</v>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>46216.625</v>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>46217.625</v>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="8" t="n">
         <v>46218.625</v>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>46218.625</v>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>46216.625</v>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>46219.625</v>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>46219.625</v>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>46219.625</v>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>46221.625</v>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>46224.625</v>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>46225.625</v>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="8" t="n">
         <v>46224.625</v>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>46225.625</v>
       </c>
     </row>
@@ -11486,7 +11486,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="8" t="n">
         <v>46228.625</v>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="8" t="n">
         <v>46229.625</v>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="8" t="n">
         <v>46229.625</v>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="8" t="n">
         <v>46230.625</v>
       </c>
     </row>
@@ -11598,7 +11598,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="8" t="n">
         <v>46232.625</v>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="8" t="n">
         <v>46232.625</v>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="8" t="n">
         <v>46233.625</v>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="8" t="n">
         <v>46237.625</v>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="8" t="n">
         <v>46237.625</v>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="8" t="n">
         <v>46244.625</v>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="8" t="n">
         <v>46244.625</v>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="8" t="n">
         <v>46244.625</v>
       </c>
     </row>
@@ -11822,7 +11822,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="8" t="n">
         <v>46248.625</v>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="8" t="n">
         <v>46249.625</v>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="8" t="n">
         <v>46251.625</v>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="8" t="n">
         <v>46255.625</v>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F70" s="8" t="n">
         <v>46256.625</v>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="8" t="n">
         <v>46257.625</v>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F72" s="8" t="n">
         <v>46261.625</v>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="8" t="n">
         <v>46261.625</v>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="8" t="n">
         <v>46260.625</v>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F75" s="8" t="n">
         <v>46262.625</v>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="8" t="n">
         <v>46288.625</v>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F77" s="7" t="n">
+      <c r="F77" s="8" t="n">
         <v>46283.625</v>
       </c>
     </row>
@@ -12158,7 +12158,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="8" t="n">
         <v>46289.625</v>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F79" s="8" t="n">
         <v>46288.625</v>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F80" s="8" t="n">
         <v>46283.625</v>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F81" s="7" t="n">
+      <c r="F81" s="8" t="n">
         <v>46289.625</v>
       </c>
     </row>
@@ -19078,7 +19078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19088,6 +19088,8 @@
     <col width="14.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19126,6 +19128,16 @@
           <t>conclusion</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>numerator_label</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>denominator_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -19161,6 +19173,16 @@
           <t>要注意</t>
         </is>
       </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>不良が報告されたロット数</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>当該サプライヤーの部品を消費したロット数</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -19194,6 +19216,16 @@
           <t>要注意</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>最終保全日からロット製造開始日までの日数</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>設備の保全間隔（日）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -19229,6 +19261,12 @@
           <t>出荷保留</t>
         </is>
       </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>NG となった検査の件数</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -19264,6 +19302,8 @@
           <t>代替検討</t>
         </is>
       </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -19299,6 +19339,16 @@
           <t>代替候補</t>
         </is>
       </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>不良が報告されたロット数</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>当該サプライヤーの部品を消費したロット数</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -19334,6 +19384,16 @@
           <t>遅延リスク</t>
         </is>
       </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>納期までの残日数</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>製造リードタイム（日）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -19369,6 +19429,12 @@
           <t>設備起因疑い</t>
         </is>
       </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>同一設備・同一不良種別で30日以内に発生した不良の件数</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -19406,6 +19472,8 @@
           <t>影響範囲</t>
         </is>
       </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kg_toolkit.xlsx
+++ b/data/kg_toolkit.xlsx
@@ -19078,7 +19078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19090,6 +19090,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19138,6 +19139,11 @@
           <t>denominator_label</t>
         </is>
       </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -19183,6 +19189,11 @@
           <t>当該サプライヤーの部品を消費したロット数</t>
         </is>
       </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>gt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -19226,6 +19237,11 @@
           <t>設備の保全間隔（日）</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>gt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -19267,6 +19283,11 @@
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -19304,6 +19325,11 @@
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>lt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -19349,6 +19375,11 @@
           <t>当該サプライヤーの部品を消費したロット数</t>
         </is>
       </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>le</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -19394,6 +19425,11 @@
           <t>製造リードタイム（日）</t>
         </is>
       </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>lt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -19435,6 +19471,11 @@
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -19474,6 +19515,7 @@
       </c>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kg_toolkit.xlsx
+++ b/data/kg_toolkit.xlsx
@@ -19158,7 +19158,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>同一サプライヤーの部品を使った直近3ロットの不良率が閾値を超える場合、当該部品を使うロットを要注意と判定する</t>
+          <t>当該サプライヤーの部品を消費した全ロットのうち、不良が報告されたロットの割合が閾値を超える場合、要注意とする</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>最終保全日から保全間隔（maint_interval_days）を超えた設備で製造したロットを要注意と判定する</t>
+          <t>ロット製造開始日以前で最も新しい保全日から製造開始日までの日数が、設備の保全間隔（maint_interval_days）を超える場合、要注意とする。製造開始日以前の保全記録がない場合は判定不能とする</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>代替サプライヤーは同一規格（spec）の部品を供給し、直近の不良率が閾値以下であること</t>
+          <t>R04 に該当するサプライヤーが供給する部品について、同一規格（spec）の部品を供給する現行以外のサプライヤーのうち、その部品を消費した全ロットに対する不良ロットの割合が閾値以下のものを代替候補とする</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">

--- a/data/kg_toolkit.xlsx
+++ b/data/kg_toolkit.xlsx
@@ -19078,7 +19078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19091,6 +19091,7 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19144,6 +19145,11 @@
           <t>comparison</t>
         </is>
       </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>min_denominator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -19158,7 +19164,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>当該サプライヤーの部品を消費した全ロットのうち、不良が報告されたロットの割合が閾値を超える場合、要注意とする</t>
+          <t>当該サプライヤーの部品を消費した全ロットのうち、不良が報告されたロットの割合が閾値を超える場合、要注意とする。消費ロット数が最小標本数（min_denominator）未満の場合は判定不能（標本数不足）とする</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -19194,6 +19200,9 @@
           <t>gt</t>
         </is>
       </c>
+      <c r="K2" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -19242,6 +19251,7 @@
           <t>gt</t>
         </is>
       </c>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -19288,6 +19298,7 @@
           <t>ge</t>
         </is>
       </c>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -19330,6 +19341,7 @@
           <t>lt</t>
         </is>
       </c>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -19344,7 +19356,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>R04 に該当するサプライヤーが供給する部品について、同一規格（spec）の部品を供給する現行以外のサプライヤーのうち、その部品を消費した全ロットに対する不良ロットの割合が閾値以下のものを代替候補とする</t>
+          <t>R04 に該当するサプライヤーが供給する部品について、同一規格（spec）かつ同一部品種別（part_type）の部品を供給する現行以外のサプライヤーのうち、その部品を消費した全ロットに対する不良ロットの割合が閾値以下のものを代替候補とする。消費ロット数が最小標本数（min_denominator）未満のサプライヤーは候補から除く</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -19380,6 +19392,9 @@
           <t>le</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -19430,6 +19445,7 @@
           <t>lt</t>
         </is>
       </c>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -19476,6 +19492,7 @@
           <t>ge</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -19516,6 +19533,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
